--- a/DEVELOPMENT_ALL_OLD_NEW/H&M/HM.0644 - C-1 + VENTURA LIGHT.xlsx
+++ b/DEVELOPMENT_ALL_OLD_NEW/H&M/HM.0644 - C-1 + VENTURA LIGHT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\TC.DEVELOPMENT.BRAND FILE 2\H&amp;M\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C21BDF-C19F-40A1-AAA2-6FAC12796FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9DCB04-8305-401D-B128-2DC059945E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="mühendisler">[1]Sayfa6!$A$2:$A$10</definedName>
     <definedName name="Müşteriler">[1]Sayfa6!$B$2:$B$20</definedName>
     <definedName name="NEW">[2]DATA!$C$2:$C$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">SABLON!$A$1:$K$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">SABLON!$A$1:$K$65</definedName>
     <definedName name="SUPERVISOR">[2]DATA!$B$2:$B$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="86">
   <si>
     <t>dcr</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>.</t>
+  </si>
+  <si>
+    <t>ACTIVITOR</t>
   </si>
 </sst>
 </file>
@@ -1572,7 +1575,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="254">
+  <cellXfs count="259">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2001,35 +2004,38 @@
     <xf numFmtId="0" fontId="52" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="53" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="53" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="53" fillId="7" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="5" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="5" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="45" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2043,31 +2049,49 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="51" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="9" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="9" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="9" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="53" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="53" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2076,81 +2100,72 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2160,28 +2175,16 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2208,151 +2211,166 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="53" fillId="7" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="42" fillId="5" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="5" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="45" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="9" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="9" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="9" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="51" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="55" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2978,7 +2996,7 @@
   <sheetPr codeName="Sayfa3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q99"/>
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="5" customWidth="1"/>
@@ -3773,21 +3791,21 @@
       <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="174">
+      <c r="C2" s="211">
         <v>46263</v>
       </c>
-      <c r="D2" s="175"/>
-      <c r="E2" s="176"/>
-      <c r="F2" s="174" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="213"/>
+      <c r="F2" s="211" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="175"/>
-      <c r="H2" s="177" t="s">
+      <c r="G2" s="212"/>
+      <c r="H2" s="214" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="178"/>
-      <c r="J2" s="178"/>
-      <c r="K2" s="179"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="216"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
@@ -3796,17 +3814,17 @@
       <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="174" t="s">
+      <c r="C3" s="211" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="175"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="180"/>
-      <c r="G3" s="181"/>
-      <c r="H3" s="186" t="s">
+      <c r="D3" s="212"/>
+      <c r="E3" s="213"/>
+      <c r="F3" s="217"/>
+      <c r="G3" s="218"/>
+      <c r="H3" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="187"/>
+      <c r="I3" s="224"/>
       <c r="J3" s="7"/>
       <c r="K3" s="8"/>
       <c r="L3" s="4"/>
@@ -3820,17 +3838,17 @@
       <c r="B4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="225" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="182"/>
-      <c r="G4" s="183"/>
-      <c r="H4" s="191"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="191"/>
-      <c r="K4" s="192"/>
+      <c r="D4" s="226"/>
+      <c r="E4" s="227"/>
+      <c r="F4" s="219"/>
+      <c r="G4" s="220"/>
+      <c r="H4" s="228"/>
+      <c r="I4" s="229"/>
+      <c r="J4" s="228"/>
+      <c r="K4" s="229"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
@@ -3839,17 +3857,17 @@
       <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="193">
+      <c r="C5" s="230">
         <v>512241879</v>
       </c>
-      <c r="D5" s="194"/>
-      <c r="E5" s="195"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="183"/>
-      <c r="H5" s="196"/>
-      <c r="I5" s="197"/>
-      <c r="J5" s="196"/>
-      <c r="K5" s="197"/>
+      <c r="D5" s="231"/>
+      <c r="E5" s="232"/>
+      <c r="F5" s="219"/>
+      <c r="G5" s="220"/>
+      <c r="H5" s="200"/>
+      <c r="I5" s="201"/>
+      <c r="J5" s="200"/>
+      <c r="K5" s="201"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
@@ -3858,17 +3876,17 @@
       <c r="B6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="198" t="s">
+      <c r="C6" s="233" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="199"/>
-      <c r="E6" s="200"/>
-      <c r="F6" s="182"/>
-      <c r="G6" s="183"/>
-      <c r="H6" s="196"/>
-      <c r="I6" s="197"/>
-      <c r="J6" s="196"/>
-      <c r="K6" s="197"/>
+      <c r="D6" s="234"/>
+      <c r="E6" s="235"/>
+      <c r="F6" s="219"/>
+      <c r="G6" s="220"/>
+      <c r="H6" s="200"/>
+      <c r="I6" s="201"/>
+      <c r="J6" s="200"/>
+      <c r="K6" s="201"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
@@ -3877,17 +3895,17 @@
       <c r="B7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="207" t="s">
+      <c r="C7" s="208" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="208"/>
-      <c r="E7" s="209"/>
-      <c r="F7" s="182"/>
-      <c r="G7" s="183"/>
-      <c r="H7" s="196"/>
-      <c r="I7" s="197"/>
-      <c r="J7" s="196"/>
-      <c r="K7" s="197"/>
+      <c r="D7" s="209"/>
+      <c r="E7" s="210"/>
+      <c r="F7" s="219"/>
+      <c r="G7" s="220"/>
+      <c r="H7" s="200"/>
+      <c r="I7" s="201"/>
+      <c r="J7" s="200"/>
+      <c r="K7" s="201"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
@@ -3896,15 +3914,15 @@
       <c r="B8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="201"/>
-      <c r="D8" s="202"/>
-      <c r="E8" s="203"/>
-      <c r="F8" s="182"/>
-      <c r="G8" s="183"/>
+      <c r="C8" s="236"/>
+      <c r="D8" s="237"/>
+      <c r="E8" s="238"/>
+      <c r="F8" s="219"/>
+      <c r="G8" s="220"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="196"/>
-      <c r="K8" s="197"/>
+      <c r="J8" s="200"/>
+      <c r="K8" s="201"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
@@ -3913,17 +3931,17 @@
       <c r="B9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="204" t="s">
+      <c r="C9" s="205" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="205"/>
-      <c r="E9" s="206"/>
-      <c r="F9" s="182"/>
-      <c r="G9" s="183"/>
+      <c r="D9" s="206"/>
+      <c r="E9" s="207"/>
+      <c r="F9" s="219"/>
+      <c r="G9" s="220"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="196"/>
-      <c r="K9" s="197"/>
+      <c r="J9" s="200"/>
+      <c r="K9" s="201"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
@@ -3932,15 +3950,15 @@
       <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="204"/>
-      <c r="D10" s="205"/>
-      <c r="E10" s="206"/>
-      <c r="F10" s="182"/>
-      <c r="G10" s="183"/>
+      <c r="C10" s="205"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="219"/>
+      <c r="G10" s="220"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="196"/>
-      <c r="K10" s="197"/>
+      <c r="J10" s="200"/>
+      <c r="K10" s="201"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
@@ -3949,15 +3967,15 @@
       <c r="B11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="210"/>
-      <c r="D11" s="211"/>
-      <c r="E11" s="212"/>
-      <c r="F11" s="182"/>
-      <c r="G11" s="183"/>
-      <c r="H11" s="196"/>
-      <c r="I11" s="197"/>
-      <c r="J11" s="196"/>
-      <c r="K11" s="197"/>
+      <c r="C11" s="202"/>
+      <c r="D11" s="203"/>
+      <c r="E11" s="204"/>
+      <c r="F11" s="219"/>
+      <c r="G11" s="220"/>
+      <c r="H11" s="200"/>
+      <c r="I11" s="201"/>
+      <c r="J11" s="200"/>
+      <c r="K11" s="201"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
@@ -3966,17 +3984,17 @@
       <c r="B12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="213" t="s">
+      <c r="C12" s="197" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="214"/>
-      <c r="E12" s="215"/>
-      <c r="F12" s="182"/>
-      <c r="G12" s="183"/>
-      <c r="H12" s="196"/>
-      <c r="I12" s="197"/>
-      <c r="J12" s="196"/>
-      <c r="K12" s="197"/>
+      <c r="D12" s="198"/>
+      <c r="E12" s="199"/>
+      <c r="F12" s="219"/>
+      <c r="G12" s="220"/>
+      <c r="H12" s="200"/>
+      <c r="I12" s="201"/>
+      <c r="J12" s="200"/>
+      <c r="K12" s="201"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
@@ -3985,15 +4003,15 @@
       <c r="B13" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="210"/>
-      <c r="D13" s="211"/>
-      <c r="E13" s="212"/>
-      <c r="F13" s="184"/>
-      <c r="G13" s="185"/>
-      <c r="H13" s="196"/>
-      <c r="I13" s="197"/>
-      <c r="J13" s="196"/>
-      <c r="K13" s="197"/>
+      <c r="C13" s="202"/>
+      <c r="D13" s="203"/>
+      <c r="E13" s="204"/>
+      <c r="F13" s="221"/>
+      <c r="G13" s="222"/>
+      <c r="H13" s="200"/>
+      <c r="I13" s="201"/>
+      <c r="J13" s="200"/>
+      <c r="K13" s="201"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
@@ -4002,17 +4020,17 @@
       <c r="B14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="216"/>
-      <c r="D14" s="216"/>
-      <c r="E14" s="217"/>
-      <c r="F14" s="218" t="s">
+      <c r="C14" s="183"/>
+      <c r="D14" s="183"/>
+      <c r="E14" s="184"/>
+      <c r="F14" s="185" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="219"/>
-      <c r="H14" s="222" t="s">
+      <c r="G14" s="186"/>
+      <c r="H14" s="189" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="223"/>
+      <c r="I14" s="190"/>
       <c r="J14" s="16"/>
       <c r="K14" s="17"/>
       <c r="L14" s="4"/>
@@ -4030,14 +4048,14 @@
       <c r="E15" s="21">
         <v>1</v>
       </c>
-      <c r="F15" s="220"/>
-      <c r="G15" s="221"/>
-      <c r="H15" s="220"/>
-      <c r="I15" s="224"/>
-      <c r="J15" s="225" t="s">
+      <c r="F15" s="187"/>
+      <c r="G15" s="188"/>
+      <c r="H15" s="187"/>
+      <c r="I15" s="191"/>
+      <c r="J15" s="192" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="227" t="s">
+      <c r="K15" s="194" t="s">
         <v>20</v>
       </c>
       <c r="L15" s="4"/>
@@ -4063,12 +4081,12 @@
       <c r="G16" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="229" t="s">
+      <c r="H16" s="196" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="229"/>
-      <c r="J16" s="226"/>
-      <c r="K16" s="228"/>
+      <c r="I16" s="196"/>
+      <c r="J16" s="193"/>
+      <c r="K16" s="195"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
     </row>
@@ -4077,15 +4095,15 @@
       <c r="B17" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="230" t="s">
+      <c r="C17" s="168" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="231"/>
-      <c r="E17" s="231"/>
-      <c r="F17" s="231"/>
-      <c r="G17" s="231"/>
-      <c r="H17" s="231"/>
-      <c r="I17" s="232"/>
+      <c r="D17" s="169"/>
+      <c r="E17" s="169"/>
+      <c r="F17" s="169"/>
+      <c r="G17" s="169"/>
+      <c r="H17" s="169"/>
+      <c r="I17" s="170"/>
       <c r="J17" s="28"/>
       <c r="K17" s="29"/>
       <c r="L17" s="25"/>
@@ -4143,10 +4161,10 @@
       <c r="G20" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="233" t="s">
+      <c r="H20" s="171" t="s">
         <v>37</v>
       </c>
-      <c r="I20" s="234"/>
+      <c r="I20" s="172"/>
       <c r="J20" s="80"/>
       <c r="K20" s="81"/>
       <c r="L20" s="25"/>
@@ -4170,10 +4188,10 @@
       <c r="G21" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="233" t="s">
+      <c r="H21" s="171" t="s">
         <v>40</v>
       </c>
-      <c r="I21" s="234"/>
+      <c r="I21" s="172"/>
       <c r="J21" s="80"/>
       <c r="K21" s="81"/>
       <c r="L21" s="25"/>
@@ -4210,10 +4228,10 @@
       <c r="G23" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="H23" s="235" t="s">
+      <c r="H23" s="175" t="s">
         <v>42</v>
       </c>
-      <c r="I23" s="235"/>
+      <c r="I23" s="175"/>
       <c r="J23" s="80"/>
       <c r="K23" s="99"/>
       <c r="L23" s="25"/>
@@ -4237,10 +4255,10 @@
       <c r="G24" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="H24" s="171" t="s">
+      <c r="H24" s="157" t="s">
         <v>44</v>
       </c>
-      <c r="I24" s="171"/>
+      <c r="I24" s="157"/>
       <c r="J24" s="100"/>
       <c r="K24" s="101"/>
       <c r="L24" s="25"/>
@@ -4260,8 +4278,8 @@
       <c r="E25" s="78"/>
       <c r="F25" s="81"/>
       <c r="G25" s="34"/>
-      <c r="H25" s="171"/>
-      <c r="I25" s="171"/>
+      <c r="H25" s="157"/>
+      <c r="I25" s="157"/>
       <c r="J25" s="100"/>
       <c r="K25" s="101"/>
       <c r="L25" s="25"/>
@@ -4296,10 +4314,10 @@
       <c r="G27" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="H27" s="235" t="s">
+      <c r="H27" s="175" t="s">
         <v>42</v>
       </c>
-      <c r="I27" s="235"/>
+      <c r="I27" s="175"/>
       <c r="J27" s="80"/>
       <c r="K27" s="99"/>
       <c r="L27" s="25"/>
@@ -4323,10 +4341,10 @@
       <c r="G28" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="H28" s="171" t="s">
+      <c r="H28" s="157" t="s">
         <v>44</v>
       </c>
-      <c r="I28" s="171"/>
+      <c r="I28" s="157"/>
       <c r="J28" s="100"/>
       <c r="K28" s="101"/>
       <c r="L28" s="25"/>
@@ -4367,10 +4385,10 @@
       <c r="G30" s="100" t="s">
         <v>36</v>
       </c>
-      <c r="H30" s="236" t="s">
+      <c r="H30" s="176" t="s">
         <v>48</v>
       </c>
-      <c r="I30" s="236"/>
+      <c r="I30" s="176"/>
       <c r="J30" s="100"/>
       <c r="K30" s="100"/>
       <c r="L30" s="25"/>
@@ -4390,8 +4408,8 @@
       <c r="E31" s="78"/>
       <c r="F31" s="100"/>
       <c r="G31" s="34"/>
-      <c r="H31" s="236"/>
-      <c r="I31" s="236"/>
+      <c r="H31" s="176"/>
+      <c r="I31" s="176"/>
       <c r="J31" s="100"/>
       <c r="K31" s="100"/>
       <c r="L31" s="25"/>
@@ -4432,10 +4450,10 @@
       <c r="G33" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="H33" s="161" t="s">
+      <c r="H33" s="162" t="s">
         <v>50</v>
       </c>
-      <c r="I33" s="162"/>
+      <c r="I33" s="163"/>
       <c r="J33" s="107"/>
       <c r="K33" s="107"/>
       <c r="L33" s="25"/>
@@ -4459,10 +4477,10 @@
       <c r="G34" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="H34" s="161" t="s">
+      <c r="H34" s="162" t="s">
         <v>52</v>
       </c>
-      <c r="I34" s="162"/>
+      <c r="I34" s="163"/>
       <c r="J34" s="107"/>
       <c r="K34" s="107"/>
       <c r="L34" s="25"/>
@@ -4503,10 +4521,10 @@
       <c r="G36" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="H36" s="237" t="s">
+      <c r="H36" s="177" t="s">
         <v>54</v>
       </c>
-      <c r="I36" s="238"/>
+      <c r="I36" s="178"/>
       <c r="J36" s="81"/>
       <c r="K36" s="81"/>
       <c r="L36" s="25"/>
@@ -4526,8 +4544,8 @@
       <c r="E37" s="78"/>
       <c r="F37" s="81"/>
       <c r="G37" s="81"/>
-      <c r="H37" s="172"/>
-      <c r="I37" s="173"/>
+      <c r="H37" s="179"/>
+      <c r="I37" s="180"/>
       <c r="J37" s="81"/>
       <c r="K37" s="81"/>
       <c r="L37" s="25"/>
@@ -4541,8 +4559,8 @@
       <c r="E38" s="41"/>
       <c r="F38" s="39"/>
       <c r="G38" s="39"/>
-      <c r="H38" s="239"/>
-      <c r="I38" s="240"/>
+      <c r="H38" s="181"/>
+      <c r="I38" s="182"/>
       <c r="J38" s="39"/>
       <c r="K38" s="39"/>
       <c r="L38" s="25"/>
@@ -4569,16 +4587,16 @@
         <v>55</v>
       </c>
       <c r="C40" s="115"/>
-      <c r="D40" s="149" t="s">
+      <c r="D40" s="173" t="s">
         <v>82</v>
       </c>
-      <c r="E40" s="150"/>
-      <c r="F40" s="150"/>
-      <c r="G40" s="151"/>
-      <c r="H40" s="149" t="s">
+      <c r="E40" s="174"/>
+      <c r="F40" s="174"/>
+      <c r="G40" s="239"/>
+      <c r="H40" s="173" t="s">
         <v>83</v>
       </c>
-      <c r="I40" s="150"/>
+      <c r="I40" s="174"/>
       <c r="J40" s="116"/>
       <c r="K40" s="116"/>
       <c r="L40" s="25"/>
@@ -4589,17 +4607,17 @@
       <c r="B41" s="117" t="s">
         <v>56</v>
       </c>
-      <c r="C41" s="165" t="s">
+      <c r="C41" s="249" t="s">
         <v>79</v>
       </c>
-      <c r="D41" s="166"/>
-      <c r="E41" s="166"/>
-      <c r="F41" s="166"/>
-      <c r="G41" s="167"/>
-      <c r="H41" s="159" t="s">
+      <c r="D41" s="250"/>
+      <c r="E41" s="250"/>
+      <c r="F41" s="250"/>
+      <c r="G41" s="251"/>
+      <c r="H41" s="160" t="s">
         <v>84</v>
       </c>
-      <c r="I41" s="160"/>
+      <c r="I41" s="161"/>
       <c r="J41" s="89"/>
       <c r="K41" s="89"/>
       <c r="L41" s="25"/>
@@ -4619,10 +4637,10 @@
       <c r="G42" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="H42" s="161" t="s">
+      <c r="H42" s="162" t="s">
         <v>58</v>
       </c>
-      <c r="I42" s="162"/>
+      <c r="I42" s="163"/>
       <c r="J42" s="120"/>
       <c r="K42" s="120"/>
       <c r="L42" s="25"/>
@@ -4640,10 +4658,10 @@
       <c r="G43" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="H43" s="161" t="s">
+      <c r="H43" s="162" t="s">
         <v>59</v>
       </c>
-      <c r="I43" s="162"/>
+      <c r="I43" s="163"/>
       <c r="J43" s="120"/>
       <c r="K43" s="120"/>
       <c r="L43" s="25"/>
@@ -4657,8 +4675,8 @@
       <c r="E44" s="78"/>
       <c r="F44" s="100"/>
       <c r="G44" s="113"/>
-      <c r="H44" s="163"/>
-      <c r="I44" s="164"/>
+      <c r="H44" s="247"/>
+      <c r="I44" s="248"/>
       <c r="J44" s="100"/>
       <c r="K44" s="100"/>
       <c r="L44" s="25"/>
@@ -4667,12 +4685,12 @@
     <row r="45" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A45" s="26"/>
       <c r="B45" s="117"/>
-      <c r="C45" s="168" t="s">
+      <c r="C45" s="252" t="s">
         <v>63</v>
       </c>
-      <c r="D45" s="169"/>
-      <c r="E45" s="169"/>
-      <c r="F45" s="170"/>
+      <c r="D45" s="253"/>
+      <c r="E45" s="253"/>
+      <c r="F45" s="254"/>
       <c r="G45" s="118"/>
       <c r="H45" s="122"/>
       <c r="I45" s="123"/>
@@ -4697,10 +4715,10 @@
       <c r="G46" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="H46" s="161" t="s">
+      <c r="H46" s="162" t="s">
         <v>58</v>
       </c>
-      <c r="I46" s="162"/>
+      <c r="I46" s="163"/>
       <c r="J46" s="80"/>
       <c r="K46" s="81"/>
       <c r="L46" s="25"/>
@@ -4718,10 +4736,10 @@
       <c r="G47" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="H47" s="171" t="s">
+      <c r="H47" s="157" t="s">
         <v>62</v>
       </c>
-      <c r="I47" s="171"/>
+      <c r="I47" s="157"/>
       <c r="J47" s="80"/>
       <c r="K47" s="81"/>
       <c r="L47" s="25"/>
@@ -4739,148 +4757,148 @@
       <c r="G48" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="H48" s="172" t="s">
+      <c r="H48" s="179" t="s">
         <v>59</v>
       </c>
-      <c r="I48" s="173"/>
+      <c r="I48" s="180"/>
       <c r="J48" s="80"/>
       <c r="K48" s="81"/>
       <c r="L48" s="25"/>
       <c r="M48" s="25"/>
     </row>
-    <row r="49" spans="1:13" ht="71.099999999999994" customHeight="1">
+    <row r="49" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A49" s="26"/>
-      <c r="B49" s="117"/>
-      <c r="C49" s="103"/>
-      <c r="D49" s="103"/>
-      <c r="E49" s="103"/>
-      <c r="F49" s="104"/>
-      <c r="G49" s="104"/>
-      <c r="H49" s="128"/>
-      <c r="I49" s="129"/>
-      <c r="J49" s="104"/>
-      <c r="K49" s="130"/>
+      <c r="B49" s="255"/>
+      <c r="C49" s="45"/>
+      <c r="D49" s="45"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="45">
+        <v>6</v>
+      </c>
+      <c r="G49" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="H49" s="256" t="s">
+        <v>85</v>
+      </c>
+      <c r="I49" s="149"/>
+      <c r="J49" s="257"/>
+      <c r="K49" s="258"/>
       <c r="L49" s="25"/>
       <c r="M49" s="25"/>
     </row>
     <row r="50" spans="1:13" ht="71.099999999999994" customHeight="1">
       <c r="A50" s="26"/>
-      <c r="B50" s="98" t="s">
-        <v>64</v>
-      </c>
-      <c r="C50" s="78">
-        <v>5</v>
-      </c>
-      <c r="D50" s="78">
-        <v>50</v>
-      </c>
-      <c r="E50" s="78">
-        <v>100</v>
-      </c>
-      <c r="F50" s="100">
-        <v>1</v>
-      </c>
-      <c r="G50" s="131" t="s">
-        <v>77</v>
-      </c>
-      <c r="H50" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="I50" s="152"/>
-      <c r="J50" s="81"/>
-      <c r="K50" s="81"/>
+      <c r="B50" s="117"/>
+      <c r="C50" s="103"/>
+      <c r="D50" s="103"/>
+      <c r="E50" s="103"/>
+      <c r="F50" s="104"/>
+      <c r="G50" s="104"/>
+      <c r="H50" s="128"/>
+      <c r="I50" s="129"/>
+      <c r="J50" s="104"/>
+      <c r="K50" s="130"/>
       <c r="L50" s="25"/>
       <c r="M50" s="25"/>
     </row>
     <row r="51" spans="1:13" ht="71.099999999999994" customHeight="1">
       <c r="A51" s="26"/>
       <c r="B51" s="98" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C51" s="78">
-        <v>2</v>
-      </c>
-      <c r="D51" s="78" t="s">
-        <v>39</v>
+        <v>5</v>
+      </c>
+      <c r="D51" s="78">
+        <v>50</v>
       </c>
       <c r="E51" s="78">
-        <v>150</v>
-      </c>
-      <c r="F51" s="81">
-        <v>50</v>
-      </c>
-      <c r="G51" s="81" t="s">
-        <v>36</v>
-      </c>
-      <c r="H51" s="171" t="s">
-        <v>66</v>
-      </c>
-      <c r="I51" s="171"/>
+        <v>100</v>
+      </c>
+      <c r="F51" s="100">
+        <v>1</v>
+      </c>
+      <c r="G51" s="131" t="s">
+        <v>77</v>
+      </c>
+      <c r="H51" s="240" t="s">
+        <v>65</v>
+      </c>
+      <c r="I51" s="240"/>
       <c r="J51" s="81"/>
       <c r="K51" s="81"/>
       <c r="L51" s="25"/>
       <c r="M51" s="25"/>
     </row>
-    <row r="52" spans="1:13" ht="77.099999999999994" customHeight="1">
+    <row r="52" spans="1:13" ht="71.099999999999994" customHeight="1">
       <c r="A52" s="26"/>
-      <c r="B52" s="117"/>
-      <c r="C52" s="103"/>
-      <c r="D52" s="103"/>
-      <c r="E52" s="103"/>
-      <c r="F52" s="104"/>
-      <c r="G52" s="104"/>
-      <c r="H52" s="128"/>
-      <c r="I52" s="129"/>
-      <c r="J52" s="104"/>
-      <c r="K52" s="130"/>
+      <c r="B52" s="98" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" s="78">
+        <v>2</v>
+      </c>
+      <c r="D52" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="E52" s="78">
+        <v>150</v>
+      </c>
+      <c r="F52" s="81">
+        <v>50</v>
+      </c>
+      <c r="G52" s="81" t="s">
+        <v>36</v>
+      </c>
+      <c r="H52" s="157" t="s">
+        <v>66</v>
+      </c>
+      <c r="I52" s="157"/>
+      <c r="J52" s="81"/>
+      <c r="K52" s="81"/>
       <c r="L52" s="25"/>
       <c r="M52" s="25"/>
     </row>
-    <row r="53" spans="1:13" ht="74.099999999999994" customHeight="1">
-      <c r="A53" s="47"/>
-      <c r="B53" s="132" t="s">
-        <v>67</v>
-      </c>
-      <c r="C53" s="133">
-        <v>7</v>
-      </c>
-      <c r="D53" s="133">
-        <v>45</v>
-      </c>
-      <c r="E53" s="133">
-        <v>80</v>
-      </c>
-      <c r="F53" s="34">
-        <v>1</v>
-      </c>
-      <c r="G53" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="H53" s="153" t="s">
-        <v>68</v>
-      </c>
-      <c r="I53" s="153"/>
-      <c r="J53" s="34"/>
-      <c r="K53" s="34"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="48"/>
+    <row r="53" spans="1:13" ht="77.099999999999994" customHeight="1">
+      <c r="A53" s="26"/>
+      <c r="B53" s="117"/>
+      <c r="C53" s="103"/>
+      <c r="D53" s="103"/>
+      <c r="E53" s="103"/>
+      <c r="F53" s="104"/>
+      <c r="G53" s="104"/>
+      <c r="H53" s="128"/>
+      <c r="I53" s="129"/>
+      <c r="J53" s="104"/>
+      <c r="K53" s="130"/>
+      <c r="L53" s="25"/>
+      <c r="M53" s="25"/>
     </row>
     <row r="54" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A54" s="47"/>
-      <c r="B54" s="132"/>
-      <c r="C54" s="133"/>
-      <c r="D54" s="133"/>
-      <c r="E54" s="133"/>
+      <c r="B54" s="132" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" s="133">
+        <v>7</v>
+      </c>
+      <c r="D54" s="133">
+        <v>45</v>
+      </c>
+      <c r="E54" s="133">
+        <v>80</v>
+      </c>
       <c r="F54" s="34">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G54" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="H54" s="242" t="s">
-        <v>69</v>
-      </c>
-      <c r="I54" s="242"/>
+      <c r="H54" s="241" t="s">
+        <v>68</v>
+      </c>
+      <c r="I54" s="241"/>
       <c r="J54" s="34"/>
       <c r="K54" s="34"/>
       <c r="L54" s="4"/>
@@ -4888,85 +4906,85 @@
     </row>
     <row r="55" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A55" s="47"/>
-      <c r="B55" s="98" t="s">
-        <v>51</v>
-      </c>
-      <c r="C55" s="78">
-        <v>2</v>
-      </c>
-      <c r="D55" s="78" t="s">
-        <v>39</v>
-      </c>
-      <c r="E55" s="78"/>
-      <c r="F55" s="81"/>
-      <c r="G55" s="81"/>
-      <c r="H55" s="243"/>
-      <c r="I55" s="243"/>
-      <c r="J55" s="81"/>
-      <c r="K55" s="81"/>
+      <c r="B55" s="132"/>
+      <c r="C55" s="133"/>
+      <c r="D55" s="133"/>
+      <c r="E55" s="133"/>
+      <c r="F55" s="34">
+        <v>20</v>
+      </c>
+      <c r="G55" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="H55" s="158" t="s">
+        <v>69</v>
+      </c>
+      <c r="I55" s="158"/>
+      <c r="J55" s="34"/>
+      <c r="K55" s="34"/>
       <c r="L55" s="4"/>
       <c r="M55" s="48"/>
     </row>
     <row r="56" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A56" s="47"/>
-      <c r="B56" s="117"/>
-      <c r="C56" s="154"/>
-      <c r="D56" s="155"/>
-      <c r="E56" s="155"/>
-      <c r="F56" s="155"/>
-      <c r="G56" s="156"/>
+      <c r="B56" s="98" t="s">
+        <v>51</v>
+      </c>
+      <c r="C56" s="78">
+        <v>2</v>
+      </c>
+      <c r="D56" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="E56" s="78"/>
+      <c r="F56" s="81"/>
+      <c r="G56" s="81"/>
       <c r="H56" s="159"/>
-      <c r="I56" s="160"/>
-      <c r="J56" s="89"/>
-      <c r="K56" s="89"/>
+      <c r="I56" s="159"/>
+      <c r="J56" s="81"/>
+      <c r="K56" s="81"/>
       <c r="L56" s="4"/>
       <c r="M56" s="48"/>
     </row>
     <row r="57" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A57" s="47"/>
-      <c r="B57" s="134" t="s">
-        <v>70</v>
-      </c>
-      <c r="C57" s="106">
-        <v>3</v>
-      </c>
-      <c r="D57" s="106">
-        <v>45</v>
-      </c>
-      <c r="E57" s="106">
-        <v>100</v>
-      </c>
-      <c r="F57" s="107">
-        <v>5</v>
-      </c>
-      <c r="G57" s="100" t="s">
-        <v>71</v>
-      </c>
-      <c r="H57" s="161" t="s">
-        <v>80</v>
-      </c>
-      <c r="I57" s="162"/>
-      <c r="J57" s="107"/>
-      <c r="K57" s="127"/>
+      <c r="B57" s="117"/>
+      <c r="C57" s="242"/>
+      <c r="D57" s="243"/>
+      <c r="E57" s="243"/>
+      <c r="F57" s="243"/>
+      <c r="G57" s="244"/>
+      <c r="H57" s="160"/>
+      <c r="I57" s="161"/>
+      <c r="J57" s="89"/>
+      <c r="K57" s="89"/>
       <c r="L57" s="4"/>
       <c r="M57" s="48"/>
     </row>
     <row r="58" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A58" s="47"/>
       <c r="B58" s="134" t="s">
-        <v>38</v>
-      </c>
-      <c r="C58" s="106"/>
-      <c r="D58" s="106"/>
-      <c r="E58" s="106"/>
-      <c r="F58" s="107"/>
+        <v>70</v>
+      </c>
+      <c r="C58" s="106">
+        <v>3</v>
+      </c>
+      <c r="D58" s="106">
+        <v>45</v>
+      </c>
+      <c r="E58" s="106">
+        <v>100</v>
+      </c>
+      <c r="F58" s="107">
+        <v>5</v>
+      </c>
       <c r="G58" s="100" t="s">
-        <v>36</v>
-      </c>
-      <c r="H58" s="109" t="s">
-        <v>72</v>
-      </c>
-      <c r="I58" s="108"/>
+        <v>71</v>
+      </c>
+      <c r="H58" s="162" t="s">
+        <v>80</v>
+      </c>
+      <c r="I58" s="163"/>
       <c r="J58" s="107"/>
       <c r="K58" s="127"/>
       <c r="L58" s="4"/>
@@ -4974,199 +4992,205 @@
     </row>
     <row r="59" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A59" s="47"/>
-      <c r="B59" s="135"/>
-      <c r="C59" s="136"/>
-      <c r="D59" s="157"/>
-      <c r="E59" s="157"/>
-      <c r="F59" s="137"/>
-      <c r="G59" s="137"/>
-      <c r="H59" s="158"/>
-      <c r="I59" s="158"/>
-      <c r="J59" s="137"/>
-      <c r="K59" s="137"/>
+      <c r="B59" s="134" t="s">
+        <v>38</v>
+      </c>
+      <c r="C59" s="106"/>
+      <c r="D59" s="106"/>
+      <c r="E59" s="106"/>
+      <c r="F59" s="107"/>
+      <c r="G59" s="100" t="s">
+        <v>36</v>
+      </c>
+      <c r="H59" s="109" t="s">
+        <v>72</v>
+      </c>
+      <c r="I59" s="108"/>
+      <c r="J59" s="107"/>
+      <c r="K59" s="127"/>
       <c r="L59" s="4"/>
       <c r="M59" s="48"/>
     </row>
     <row r="60" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A60" s="47"/>
-      <c r="B60" s="138" t="s">
-        <v>73</v>
-      </c>
-      <c r="C60" s="139">
-        <v>2</v>
-      </c>
-      <c r="D60" s="140" t="s">
-        <v>39</v>
-      </c>
-      <c r="E60" s="140">
-        <v>80</v>
-      </c>
-      <c r="F60" s="141">
-        <v>2</v>
-      </c>
-      <c r="G60" s="113" t="s">
-        <v>74</v>
-      </c>
-      <c r="H60" s="245" t="s">
-        <v>75</v>
-      </c>
-      <c r="I60" s="245"/>
-      <c r="J60" s="142"/>
-      <c r="K60" s="143"/>
+      <c r="B60" s="135"/>
+      <c r="C60" s="136"/>
+      <c r="D60" s="245"/>
+      <c r="E60" s="245"/>
+      <c r="F60" s="137"/>
+      <c r="G60" s="137"/>
+      <c r="H60" s="246"/>
+      <c r="I60" s="246"/>
+      <c r="J60" s="137"/>
+      <c r="K60" s="137"/>
       <c r="L60" s="4"/>
       <c r="M60" s="48"/>
     </row>
     <row r="61" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A61" s="47"/>
-      <c r="B61" s="144" t="s">
-        <v>76</v>
-      </c>
-      <c r="C61" s="142"/>
-      <c r="D61" s="142"/>
-      <c r="E61" s="142"/>
-      <c r="F61" s="145"/>
-      <c r="G61" s="143"/>
-      <c r="H61" s="246"/>
-      <c r="I61" s="246"/>
+      <c r="B61" s="138" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" s="139">
+        <v>2</v>
+      </c>
+      <c r="D61" s="140" t="s">
+        <v>39</v>
+      </c>
+      <c r="E61" s="140">
+        <v>80</v>
+      </c>
+      <c r="F61" s="141">
+        <v>2</v>
+      </c>
+      <c r="G61" s="113" t="s">
+        <v>74</v>
+      </c>
+      <c r="H61" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="I61" s="165"/>
       <c r="J61" s="142"/>
-      <c r="K61" s="142"/>
+      <c r="K61" s="143"/>
       <c r="L61" s="4"/>
       <c r="M61" s="48"/>
     </row>
     <row r="62" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A62" s="47"/>
-      <c r="B62" s="146"/>
-      <c r="C62" s="147"/>
-      <c r="D62" s="147"/>
-      <c r="E62" s="147"/>
-      <c r="F62" s="148"/>
-      <c r="G62" s="148"/>
-      <c r="H62" s="244"/>
-      <c r="I62" s="244"/>
-      <c r="J62" s="148"/>
-      <c r="K62" s="148"/>
+      <c r="B62" s="144" t="s">
+        <v>76</v>
+      </c>
+      <c r="C62" s="142"/>
+      <c r="D62" s="142"/>
+      <c r="E62" s="142"/>
+      <c r="F62" s="145"/>
+      <c r="G62" s="143"/>
+      <c r="H62" s="166"/>
+      <c r="I62" s="166"/>
+      <c r="J62" s="142"/>
+      <c r="K62" s="142"/>
       <c r="L62" s="4"/>
       <c r="M62" s="48"/>
     </row>
     <row r="63" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A63" s="47"/>
-      <c r="B63" s="49"/>
-      <c r="C63" s="50"/>
-      <c r="D63" s="51"/>
-      <c r="E63" s="51"/>
-      <c r="F63" s="52"/>
-      <c r="G63" s="44"/>
-      <c r="H63" s="247"/>
-      <c r="I63" s="247"/>
-      <c r="J63" s="43"/>
-      <c r="K63" s="46"/>
+      <c r="B63" s="146"/>
+      <c r="C63" s="147"/>
+      <c r="D63" s="147"/>
+      <c r="E63" s="147"/>
+      <c r="F63" s="148"/>
+      <c r="G63" s="148"/>
+      <c r="H63" s="164"/>
+      <c r="I63" s="164"/>
+      <c r="J63" s="148"/>
+      <c r="K63" s="148"/>
       <c r="L63" s="4"/>
       <c r="M63" s="48"/>
     </row>
     <row r="64" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A64" s="47"/>
       <c r="B64" s="49"/>
-      <c r="C64" s="53"/>
-      <c r="D64" s="53"/>
-      <c r="E64" s="54"/>
-      <c r="F64" s="55"/>
-      <c r="G64" s="46"/>
-      <c r="H64" s="241"/>
-      <c r="I64" s="241"/>
+      <c r="C64" s="50"/>
+      <c r="D64" s="51"/>
+      <c r="E64" s="51"/>
+      <c r="F64" s="52"/>
+      <c r="G64" s="44"/>
+      <c r="H64" s="167"/>
+      <c r="I64" s="167"/>
       <c r="J64" s="43"/>
-      <c r="K64" s="43"/>
+      <c r="K64" s="46"/>
       <c r="L64" s="4"/>
       <c r="M64" s="48"/>
     </row>
     <row r="65" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A65" s="47"/>
-      <c r="B65" s="56"/>
-      <c r="C65" s="57"/>
-      <c r="D65" s="57"/>
-      <c r="E65" s="57"/>
-      <c r="F65" s="58"/>
-      <c r="G65" s="58"/>
-      <c r="H65" s="250"/>
-      <c r="I65" s="250"/>
-      <c r="J65" s="59"/>
-      <c r="K65" s="59"/>
+      <c r="B65" s="49"/>
+      <c r="C65" s="53"/>
+      <c r="D65" s="53"/>
+      <c r="E65" s="54"/>
+      <c r="F65" s="55"/>
+      <c r="G65" s="46"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="43"/>
+      <c r="K65" s="43"/>
       <c r="L65" s="4"/>
       <c r="M65" s="48"/>
     </row>
     <row r="66" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A66" s="47"/>
-      <c r="B66" s="60"/>
-      <c r="C66" s="61"/>
-      <c r="D66" s="61"/>
-      <c r="E66" s="61"/>
-      <c r="F66" s="61"/>
-      <c r="G66" s="61"/>
-      <c r="H66" s="251"/>
-      <c r="I66" s="252"/>
-      <c r="J66" s="62"/>
-      <c r="K66" s="61"/>
+      <c r="B66" s="56"/>
+      <c r="C66" s="57"/>
+      <c r="D66" s="57"/>
+      <c r="E66" s="57"/>
+      <c r="F66" s="58"/>
+      <c r="G66" s="58"/>
+      <c r="H66" s="152"/>
+      <c r="I66" s="152"/>
+      <c r="J66" s="59"/>
+      <c r="K66" s="59"/>
       <c r="L66" s="4"/>
       <c r="M66" s="48"/>
     </row>
     <row r="67" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A67" s="47"/>
-      <c r="B67" s="63"/>
-      <c r="C67" s="42"/>
-      <c r="D67" s="42"/>
-      <c r="E67" s="42"/>
-      <c r="F67" s="42"/>
-      <c r="G67" s="42"/>
-      <c r="H67" s="248"/>
-      <c r="I67" s="249"/>
-      <c r="J67" s="64"/>
-      <c r="K67" s="42"/>
+      <c r="B67" s="60"/>
+      <c r="C67" s="61"/>
+      <c r="D67" s="61"/>
+      <c r="E67" s="61"/>
+      <c r="F67" s="61"/>
+      <c r="G67" s="61"/>
+      <c r="H67" s="153"/>
+      <c r="I67" s="154"/>
+      <c r="J67" s="62"/>
+      <c r="K67" s="61"/>
       <c r="L67" s="4"/>
       <c r="M67" s="48"/>
     </row>
     <row r="68" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A68" s="47"/>
-      <c r="B68" s="45"/>
-      <c r="C68" s="45"/>
-      <c r="D68" s="45"/>
-      <c r="E68" s="45"/>
-      <c r="F68" s="45"/>
-      <c r="G68" s="45"/>
-      <c r="H68" s="253"/>
-      <c r="I68" s="253"/>
-      <c r="J68" s="65"/>
-      <c r="K68" s="45"/>
+      <c r="B68" s="63"/>
+      <c r="C68" s="42"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="42"/>
+      <c r="F68" s="42"/>
+      <c r="G68" s="42"/>
+      <c r="H68" s="150"/>
+      <c r="I68" s="151"/>
+      <c r="J68" s="64"/>
+      <c r="K68" s="42"/>
       <c r="L68" s="4"/>
-      <c r="M68" s="4"/>
+      <c r="M68" s="48"/>
     </row>
     <row r="69" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A69" s="47"/>
-      <c r="B69" s="66"/>
-      <c r="C69" s="42"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="42"/>
-      <c r="F69" s="42"/>
-      <c r="G69" s="42"/>
-      <c r="H69" s="248"/>
-      <c r="I69" s="249"/>
-      <c r="J69" s="64"/>
-      <c r="K69" s="67"/>
+      <c r="B69" s="45"/>
+      <c r="C69" s="45"/>
+      <c r="D69" s="45"/>
+      <c r="E69" s="45"/>
+      <c r="F69" s="45"/>
+      <c r="G69" s="45"/>
+      <c r="H69" s="155"/>
+      <c r="I69" s="155"/>
+      <c r="J69" s="65"/>
+      <c r="K69" s="45"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
     </row>
-    <row r="70" spans="1:13" ht="61.2">
-      <c r="A70" s="4"/>
-      <c r="B70" s="68"/>
+    <row r="70" spans="1:13" ht="74.099999999999994" customHeight="1">
+      <c r="A70" s="47"/>
+      <c r="B70" s="66"/>
       <c r="C70" s="42"/>
       <c r="D70" s="42"/>
       <c r="E70" s="42"/>
       <c r="F70" s="42"/>
       <c r="G70" s="42"/>
-      <c r="H70" s="248"/>
-      <c r="I70" s="249"/>
+      <c r="H70" s="150"/>
+      <c r="I70" s="151"/>
       <c r="J70" s="64"/>
       <c r="K70" s="67"/>
-      <c r="L70" s="69"/>
-      <c r="M70" s="70"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
     </row>
     <row r="71" spans="1:13" ht="61.2">
       <c r="A71" s="4"/>
@@ -5176,8 +5200,8 @@
       <c r="E71" s="42"/>
       <c r="F71" s="42"/>
       <c r="G71" s="42"/>
-      <c r="H71" s="248"/>
-      <c r="I71" s="249"/>
+      <c r="H71" s="150"/>
+      <c r="I71" s="151"/>
       <c r="J71" s="64"/>
       <c r="K71" s="67"/>
       <c r="L71" s="69"/>
@@ -5191,30 +5215,42 @@
       <c r="E72" s="42"/>
       <c r="F72" s="42"/>
       <c r="G72" s="42"/>
-      <c r="H72" s="248"/>
-      <c r="I72" s="249"/>
+      <c r="H72" s="150"/>
+      <c r="I72" s="151"/>
       <c r="J72" s="64"/>
       <c r="K72" s="67"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
-    </row>
-    <row r="73" spans="1:13">
+      <c r="L72" s="69"/>
+      <c r="M72" s="70"/>
+    </row>
+    <row r="73" spans="1:13" ht="61.2">
       <c r="A73" s="4"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="4"/>
+      <c r="B73" s="68"/>
+      <c r="C73" s="42"/>
+      <c r="D73" s="42"/>
+      <c r="E73" s="42"/>
+      <c r="F73" s="42"/>
+      <c r="G73" s="42"/>
+      <c r="H73" s="150"/>
+      <c r="I73" s="151"/>
+      <c r="J73" s="64"/>
+      <c r="K73" s="67"/>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="4"/>
@@ -5291,26 +5327,65 @@
     <row r="99" spans="1:1">
       <c r="A99" s="4"/>
     </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="88">
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="D40:G40"/>
     <mergeCell ref="H51:I51"/>
     <mergeCell ref="H54:I54"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="D60:E60"/>
     <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="C45:F45"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:G13"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:G15"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="H16:I16"/>
     <mergeCell ref="C17:I17"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="H21:I21"/>
@@ -5327,60 +5402,24 @@
     <mergeCell ref="H34:I34"/>
     <mergeCell ref="H37:I37"/>
     <mergeCell ref="H38:I38"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:G15"/>
-    <mergeCell ref="H14:I15"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F3:G13"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="C45:F45"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="H71:I71"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
